--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:08:00+00:00</t>
+    <t>2025-05-12T08:18:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:18:40+00:00</t>
+    <t>2025-05-12T08:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:26:30+00:00</t>
+    <t>2025-05-12T09:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T09:15:35+00:00</t>
+    <t>2025-05-12T09:44:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T09:44:35+00:00</t>
+    <t>2025-05-12T09:48:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T09:48:13+00:00</t>
+    <t>2025-05-12T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T10:07:46+00:00</t>
+    <t>2025-05-12T12:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T12:08:59+00:00</t>
+    <t>2025-05-12T12:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T12:21:25+00:00</t>
+    <t>2025-05-12T12:41:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T12:41:16+00:00</t>
+    <t>2025-05-12T13:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T13:04:33+00:00</t>
+    <t>2025-05-12T14:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1492,7 +1492,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/vitals/ValueSet/bpmeasbodylocationprecoord</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-spo2-body-location</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1522,7 +1522,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/vitals/ValueSet/bpMeasMethodVS</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-bp-meas-method</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -2712,7 +2712,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.00390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.95703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.4453125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T14:29:06+00:00</t>
+    <t>2025-05-12T14:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T14:37:35+00:00</t>
+    <t>2025-05-12T15:04:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T15:04:22+00:00</t>
+    <t>2025-05-13T10:20:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:20:58+00:00</t>
+    <t>2025-05-20T13:44:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:44:07+00:00</t>
+    <t>2025-05-20T13:46:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:46:53+00:00</t>
+    <t>2025-05-20T13:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:54:28+00:00</t>
+    <t>2025-05-20T13:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:56:00+00:00</t>
+    <t>2025-05-23T16:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T16:42:05+00:00</t>
+    <t>2025-05-23T16:51:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T16:51:26+00:00</t>
+    <t>2025-05-24T07:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-24T07:13:38+00:00</t>
+    <t>2025-05-26T07:36:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T07:36:52+00:00</t>
+    <t>2025-05-28T11:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
